--- a/財務管理系統.xlsx
+++ b/財務管理系統.xlsx
@@ -39,7 +39,7 @@
     <numFmt numFmtId="170" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="171" formatCode="0.000"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="48">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -326,6 +326,34 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -547,7 +575,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1116,6 +1144,43 @@
     <xf numFmtId="3" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1653,7 +1718,7 @@
         </is>
       </c>
       <c r="C2" s="111" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D2" s="121" t="inlineStr">
         <is>
@@ -2086,15 +2151,15 @@
   <dimension ref="A1:P633"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25"/>
   <cols>
-    <col width="10" customWidth="1" style="113" min="1" max="4"/>
+    <col width="11" customWidth="1" style="113" min="1" max="4"/>
     <col width="12" customWidth="1" style="113" min="5" max="6"/>
     <col width="16" customWidth="1" style="113" min="7" max="7"/>
-    <col width="24" customWidth="1" style="113" min="8" max="8"/>
+    <col width="34.7" customWidth="1" style="113" min="8" max="8"/>
     <col width="3" customWidth="1" style="113" min="9" max="10"/>
     <col width="11" customWidth="1" style="113" min="11" max="11"/>
     <col width="10" customWidth="1" style="113" min="12" max="12"/>
     <col width="11" customWidth="1" style="113" min="13" max="13"/>
-    <col width="32" customWidth="1" style="113" min="14" max="14"/>
+    <col width="36" customWidth="1" style="113" min="14" max="14"/>
     <col width="4" customWidth="1" style="113" min="15" max="16"/>
   </cols>
   <sheetData>
@@ -2120,6 +2185,7 @@
       <c r="O1" s="115" t="n"/>
       <c r="P1" s="116" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3" ht="21.75" customHeight="1" s="113">
       <c r="A3" s="124" t="inlineStr">
         <is>
@@ -2170,6 +2236,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="21.75" customHeight="1" s="113">
       <c r="A9" s="124" t="inlineStr">
         <is>
@@ -15980,6 +16047,7 @@
   <autoFilter ref="K11:N633"/>
   <mergeCells count="17">
     <mergeCell ref="A9:H9"/>
+    <mergeCell ref="B72:H72"/>
     <mergeCell ref="B7:P7"/>
     <mergeCell ref="B6:P6"/>
     <mergeCell ref="A66:C66"/>
@@ -15989,11 +16057,10 @@
     <mergeCell ref="B5:P5"/>
     <mergeCell ref="B69:H69"/>
     <mergeCell ref="B70:H70"/>
-    <mergeCell ref="B4:P4"/>
     <mergeCell ref="A68:H68"/>
     <mergeCell ref="G66:H66"/>
     <mergeCell ref="A3:P3"/>
-    <mergeCell ref="B72:H72"/>
+    <mergeCell ref="B4:P4"/>
     <mergeCell ref="K10:N10"/>
     <mergeCell ref="K9:N9"/>
   </mergeCells>
@@ -16040,6 +16107,7 @@
       <c r="C1" s="115" t="n"/>
       <c r="D1" s="116" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="113">
       <c r="A3" s="122" t="inlineStr">
         <is>
@@ -16059,6 +16127,7 @@
       <c r="C4" s="118" t="n"/>
       <c r="D4" s="119" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="113">
       <c r="A6" s="137" t="inlineStr">
         <is>
@@ -16072,6 +16141,7 @@
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="21.75" customHeight="1" s="113">
       <c r="A9" s="124" t="inlineStr">
         <is>
@@ -16428,6 +16498,7 @@
         <v/>
       </c>
     </row>
+    <row r="29"/>
     <row r="30" ht="21.75" customHeight="1" s="113">
       <c r="A30" s="124" t="inlineStr">
         <is>
@@ -16490,6 +16561,7 @@
         <v/>
       </c>
     </row>
+    <row r="35"/>
     <row r="36" ht="21.75" customHeight="1" s="113">
       <c r="A36" s="124" t="inlineStr">
         <is>
@@ -16509,6 +16581,7 @@
       <c r="C37" s="118" t="n"/>
       <c r="D37" s="119" t="n"/>
     </row>
+    <row r="38"/>
     <row r="39" ht="36" customHeight="1" s="113">
       <c r="A39" s="112" t="inlineStr">
         <is>
@@ -16565,6 +16638,7 @@
       <c r="D1" s="115" t="n"/>
       <c r="E1" s="116" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3" ht="21.75" customHeight="1" s="113">
       <c r="A3" s="124" t="inlineStr">
         <is>
@@ -16597,6 +16671,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="21.75" customHeight="1" s="113">
       <c r="A8" s="124" t="inlineStr">
         <is>
@@ -17136,10 +17211,10 @@
   <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25"/>
   <cols>
-    <col width="4" customWidth="1" style="113" min="1" max="1"/>
+    <col width="6" customWidth="1" style="113" min="1" max="1"/>
     <col width="28" customWidth="1" style="113" min="2" max="2"/>
     <col width="16" customWidth="1" style="113" min="3" max="3"/>
-    <col width="38" customWidth="1" style="113" min="4" max="4"/>
+    <col width="44" customWidth="1" style="113" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1" s="113">
@@ -17279,7 +17354,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="27.75" customHeight="1" s="113">
+    <row r="12" ht="32" customHeight="1" s="113">
       <c r="A12" s="17" t="n">
         <v>4</v>
       </c>
@@ -17291,7 +17366,7 @@
       <c r="C12" s="158" t="n">
         <v>1477277</v>
       </c>
-      <c r="D12" s="117" t="inlineStr">
+      <c r="D12" s="202" t="inlineStr">
         <is>
           <t>＝0050/0052/摩根新興科技基金市值加總（每日自動更新，明細見「股票部位」分頁；上傳此檔後請等下次每日自動更新或手動觸發daily-nav-update.yml取得即時市值）</t>
         </is>
@@ -17345,6 +17420,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="21.75" customHeight="1" s="113">
       <c r="A17" s="124" t="inlineStr">
         <is>
@@ -17519,6 +17595,7 @@
       </c>
       <c r="D26" s="128" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28" ht="21.75" customHeight="1" s="113">
       <c r="A28" s="124" t="inlineStr">
         <is>
@@ -17576,6 +17653,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33" ht="21.75" customHeight="1" s="113">
       <c r="A33" s="124" t="inlineStr">
         <is>
@@ -17607,6 +17685,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="147" t="inlineStr">
         <is>
@@ -17622,7 +17701,7 @@
       </c>
       <c r="C39" s="164" t="inlineStr">
         <is>
-          <t>尚未執行過自動更新</t>
+          <t>2026-09-17 17:44（手動設定，等排程修好後會改回自動更新）</t>
         </is>
       </c>
     </row>
@@ -17634,7 +17713,7 @@
       </c>
       <c r="C40" s="164" t="inlineStr">
         <is>
-          <t>MoneyDJ（基金淨值）／台灣銀行牌告匯率（即期買賣中價）</t>
+          <t>MoneyDJ（基金淨值）／台灣銀行牌告匯率（USD/TWD匯率）</t>
         </is>
       </c>
     </row>
@@ -17688,7 +17767,7 @@
   <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25"/>
   <cols>
-    <col width="4" customWidth="1" style="113" min="1" max="1"/>
+    <col width="6" customWidth="1" style="113" min="1" max="1"/>
     <col width="22" customWidth="1" style="113" min="2" max="2"/>
     <col width="8" customWidth="1" style="113" min="3" max="3"/>
     <col width="12" customWidth="1" style="113" min="4" max="4"/>
@@ -17698,6 +17777,7 @@
     <col width="13" customWidth="1" style="113" min="8" max="8"/>
     <col width="10" customWidth="1" style="113" min="9" max="9"/>
     <col width="13" customWidth="1" style="113" min="10" max="11"/>
+    <col width="13" customWidth="1" style="113" min="11" max="11"/>
     <col width="14" customWidth="1" style="113" min="12" max="12"/>
     <col width="50" customWidth="1" style="113" min="13" max="13"/>
   </cols>
@@ -17721,6 +17801,7 @@
       <c r="L1" s="115" t="n"/>
       <c r="M1" s="116" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3" ht="21.75" customHeight="1" s="113">
       <c r="A3" s="124" t="inlineStr">
         <is>
@@ -18098,6 +18179,7 @@
       </c>
       <c r="M10" s="128" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12" ht="21.75" customHeight="1" s="113">
       <c r="A12" s="124" t="inlineStr">
         <is>
@@ -18176,7 +18258,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="113">
+    <row r="14" ht="32" customHeight="1" s="113">
       <c r="A14" s="30" t="n">
         <v>1</v>
       </c>
@@ -18215,13 +18297,13 @@
         <f>IF(H14="",E14,E14*MAX(0,F14*12-I14)/(F14*12))</f>
         <v/>
       </c>
-      <c r="M14" s="22" t="inlineStr">
+      <c r="M14" s="203" t="inlineStr">
         <is>
           <t>平準型，保障20年，保費58萬；起始日同北區理財型房貸</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="113">
+    <row r="15" ht="32" customHeight="1" s="113">
       <c r="A15" s="39" t="n">
         <v>2</v>
       </c>
@@ -18260,7 +18342,7 @@
         <f>IF(H15="",E15,E15*MAX(0,F15*12-I15)/(F15*12))</f>
         <v/>
       </c>
-      <c r="M15" s="26" t="inlineStr">
+      <c r="M15" s="204" t="inlineStr">
         <is>
           <t>平準型，保障25年；總保費82萬9249元與弟弟共同分攤，本人負擔41萬4625元；起始日同東區房貸</t>
         </is>
@@ -18294,6 +18376,7 @@
       </c>
       <c r="M16" s="128" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18" ht="21.75" customHeight="1" s="113">
       <c r="A18" s="124" t="inlineStr">
         <is>
@@ -18335,6 +18418,7 @@
       <c r="L19" s="128" t="n"/>
       <c r="M19" s="128" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21" ht="21.75" customHeight="1" s="113">
       <c r="A21" s="124" t="inlineStr">
         <is>
@@ -18414,8 +18498,9 @@
   <dimension ref="A1:Q59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25"/>
   <cols>
-    <col width="6" customWidth="1" style="113" min="1" max="1"/>
+    <col width="7" customWidth="1" style="113" min="1" max="1"/>
     <col width="11" customWidth="1" style="113" min="2" max="3"/>
+    <col width="13" customWidth="1" style="113" min="3" max="3"/>
     <col width="13" customWidth="1" style="113" min="4" max="4"/>
     <col width="11" customWidth="1" style="113" min="5" max="5"/>
     <col width="13" customWidth="1" style="113" min="6" max="6"/>
@@ -18424,9 +18509,10 @@
     <col width="11" customWidth="1" style="113" min="9" max="9"/>
     <col width="30" customWidth="1" style="113" min="10" max="10"/>
     <col hidden="1" width="10" customWidth="1" style="113" min="11" max="11"/>
+    <col width="13" customWidth="1" style="113" min="12" max="12"/>
     <col hidden="1" width="6" customWidth="1" style="113" min="13" max="13"/>
-    <col hidden="1" width="8" customWidth="1" style="113" min="16" max="16"/>
-    <col hidden="1" width="6" customWidth="1" style="113" min="17" max="17"/>
+    <col hidden="1" width="36" customWidth="1" style="113" min="16" max="16"/>
+    <col hidden="1" width="8" customWidth="1" style="113" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1" s="113">
@@ -19023,6 +19109,7 @@
       <c r="K16" s="128" t="n"/>
       <c r="L16" s="128" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18" ht="21.75" customHeight="1" s="113">
       <c r="A18" s="124" t="inlineStr">
         <is>
@@ -20384,6 +20471,7 @@
         <v/>
       </c>
     </row>
+    <row r="52"/>
     <row r="53" ht="21.75" customHeight="1" s="113">
       <c r="A53" s="124" t="inlineStr">
         <is>
@@ -20437,6 +20525,7 @@
         <v/>
       </c>
     </row>
+    <row r="55"/>
     <row r="56" ht="21.75" customHeight="1" s="113">
       <c r="A56" s="124" t="inlineStr">
         <is>
@@ -20542,13 +20631,15 @@
   <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25"/>
   <cols>
-    <col width="5" customWidth="1" style="113" min="1" max="1"/>
+    <col width="6" customWidth="1" style="113" min="1" max="1"/>
     <col width="10" customWidth="1" style="113" min="2" max="2"/>
-    <col width="9" customWidth="1" style="113" min="3" max="3"/>
+    <col width="10" customWidth="1" style="113" min="3" max="3"/>
     <col width="10" customWidth="1" style="113" min="4" max="4"/>
     <col width="11" customWidth="1" style="113" min="5" max="5"/>
     <col width="9" customWidth="1" style="113" min="6" max="7"/>
+    <col width="13" customWidth="1" style="113" min="7" max="7"/>
     <col width="10" customWidth="1" style="113" min="8" max="9"/>
+    <col width="13" customWidth="1" style="113" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1" s="113">
@@ -20566,6 +20657,7 @@
       <c r="H1" s="115" t="n"/>
       <c r="I1" s="116" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3" ht="21.75" customHeight="1" s="113">
       <c r="A3" s="124" t="inlineStr">
         <is>
@@ -20945,6 +21037,7 @@
       <c r="H14" s="128" t="n"/>
       <c r="I14" s="128" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16" ht="21.75" customHeight="1" s="113">
       <c r="A16" s="124" t="inlineStr">
         <is>
@@ -21124,6 +21217,7 @@
       <c r="H21" s="128" t="n"/>
       <c r="I21" s="128" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23" ht="21.75" customHeight="1" s="113">
       <c r="A23" s="124" t="inlineStr">
         <is>
@@ -21161,6 +21255,7 @@
       <c r="H24" s="118" t="n"/>
       <c r="I24" s="119" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26" ht="21.75" customHeight="1" s="113">
       <c r="A26" s="124" t="inlineStr">
         <is>
@@ -21211,7 +21306,7 @@
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" style="113" min="1" max="1"/>
+    <col width="30" customWidth="1" style="113" min="1" max="1"/>
     <col width="26" customWidth="1" style="113" min="2" max="2"/>
     <col width="12" customWidth="1" style="113" min="3" max="3"/>
     <col width="14" customWidth="1" style="113" min="4" max="4"/>
@@ -21223,7 +21318,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="193" t="inlineStr">
+      <c r="A1" s="205" t="inlineStr">
         <is>
           <t>📊 股票／基金部位（本人）</t>
         </is>
@@ -21236,181 +21331,182 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="113">
-      <c r="A4" s="195" t="inlineStr">
+      <c r="A4" s="206" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B4" s="195" t="inlineStr">
+      <c r="B4" s="206" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C4" s="195" t="inlineStr">
+      <c r="C4" s="206" t="inlineStr">
         <is>
           <t>持有數量</t>
         </is>
       </c>
-      <c r="D4" s="195" t="inlineStr">
+      <c r="D4" s="206" t="inlineStr">
         <is>
           <t>均價／申購淨值</t>
         </is>
       </c>
-      <c r="E4" s="195" t="inlineStr">
+      <c r="E4" s="206" t="inlineStr">
         <is>
           <t>最新價格／淨值</t>
         </is>
       </c>
-      <c r="F4" s="195" t="inlineStr">
+      <c r="F4" s="206" t="inlineStr">
         <is>
           <t>市值</t>
         </is>
       </c>
-      <c r="G4" s="195" t="inlineStr">
+      <c r="G4" s="206" t="inlineStr">
         <is>
           <t>未實現損益</t>
         </is>
       </c>
-      <c r="H4" s="195" t="inlineStr">
+      <c r="H4" s="206" t="inlineStr">
         <is>
           <t>價格日期</t>
         </is>
       </c>
-      <c r="I4" s="195" t="inlineStr">
+      <c r="I4" s="206" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="196" t="inlineStr">
+      <c r="A5" s="207" t="inlineStr">
         <is>
           <t>0050</t>
         </is>
       </c>
-      <c r="B5" s="196" t="inlineStr">
+      <c r="B5" s="207" t="inlineStr">
         <is>
           <t>元大台灣50</t>
         </is>
       </c>
-      <c r="C5" s="197" t="n">
+      <c r="C5" s="208" t="n">
         <v>8000</v>
       </c>
-      <c r="D5" s="198" t="n">
+      <c r="D5" s="209" t="n">
         <v>64.92</v>
       </c>
-      <c r="E5" s="198" t="n">
+      <c r="E5" s="209" t="n">
         <v>64.92</v>
       </c>
-      <c r="F5" s="197">
+      <c r="F5" s="210">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="197">
+      <c r="G5" s="210">
         <f>(E5-D5)*C5</f>
         <v/>
       </c>
-      <c r="H5" s="196" t="inlineStr">
+      <c r="H5" s="211" t="inlineStr">
         <is>
           <t>尚未自動更新</t>
         </is>
       </c>
-      <c r="I5" s="199" t="inlineStr">
+      <c r="I5" s="212" t="inlineStr">
         <is>
           <t>－（等待每日自動更新或手動觸發daily-nav-update.yml）</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="196" t="inlineStr">
+      <c r="A6" s="207" t="inlineStr">
         <is>
           <t>0052</t>
         </is>
       </c>
-      <c r="B6" s="196" t="inlineStr">
+      <c r="B6" s="207" t="inlineStr">
         <is>
           <t>富邦科技</t>
         </is>
       </c>
-      <c r="C6" s="197" t="n">
+      <c r="C6" s="208" t="n">
         <v>12000</v>
       </c>
-      <c r="D6" s="198" t="n">
+      <c r="D6" s="209" t="n">
         <v>35.66</v>
       </c>
-      <c r="E6" s="198" t="n">
+      <c r="E6" s="209" t="n">
         <v>35.66</v>
       </c>
-      <c r="F6" s="197">
+      <c r="F6" s="210">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="197">
+      <c r="G6" s="210">
         <f>(E6-D6)*C6</f>
         <v/>
       </c>
-      <c r="H6" s="196" t="inlineStr">
+      <c r="H6" s="211" t="inlineStr">
         <is>
           <t>尚未自動更新</t>
         </is>
       </c>
-      <c r="I6" s="199" t="inlineStr">
+      <c r="I6" s="212" t="inlineStr">
         <is>
           <t>－（等待每日自動更新或手動觸發daily-nav-update.yml）</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="196" t="inlineStr">
+      <c r="A7" s="207" t="inlineStr">
         <is>
           <t>摩根新興科技證券投資信託基金</t>
         </is>
       </c>
-      <c r="B7" s="196" t="inlineStr">
+      <c r="B7" s="207" t="inlineStr">
         <is>
           <t>摩根新興科技基金-一般型</t>
         </is>
       </c>
-      <c r="C7" s="197" t="n">
+      <c r="C7" s="208" t="n">
         <v>1091</v>
       </c>
-      <c r="D7" s="198" t="n">
+      <c r="D7" s="209" t="n">
         <v>485.79</v>
       </c>
-      <c r="E7" s="198" t="n">
+      <c r="E7" s="209" t="n">
         <v>485.79</v>
       </c>
-      <c r="F7" s="197">
+      <c r="F7" s="210">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="197">
+      <c r="G7" s="210">
         <f>(E7-D7)*C7</f>
         <v/>
       </c>
-      <c r="H7" s="196" t="inlineStr">
+      <c r="H7" s="211" t="inlineStr">
         <is>
           <t>尚未自動更新</t>
         </is>
       </c>
-      <c r="I7" s="199" t="inlineStr">
+      <c r="I7" s="212" t="inlineStr">
         <is>
           <t>－（等待每日自動更新或手動觸發daily-nav-update.yml）</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="200" t="inlineStr">
+      <c r="B8" s="213" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="F8" s="201">
+      <c r="F8" s="214">
         <f>SUM(F5:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="201">
+      <c r="G8" s="214">
         <f>SUM(G5:G7)</f>
         <v/>
       </c>
@@ -21433,7 +21529,7 @@
   <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25"/>
   <cols>
-    <col width="4" customWidth="1" style="113" min="1" max="1"/>
+    <col width="6" customWidth="1" style="113" min="1" max="1"/>
     <col width="30" customWidth="1" style="113" min="2" max="2"/>
     <col width="14" customWidth="1" style="113" min="3" max="3"/>
     <col width="48" customWidth="1" style="113" min="4" max="4"/>
@@ -21449,6 +21545,7 @@
       <c r="C1" s="115" t="n"/>
       <c r="D1" s="116" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3" ht="21.75" customHeight="1" s="113">
       <c r="A3" s="124" t="inlineStr">
         <is>
@@ -21564,7 +21661,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="113">
+    <row r="11" ht="32" customHeight="1" s="113">
       <c r="A11" s="17" t="n">
         <v>4</v>
       </c>
@@ -21577,7 +21674,7 @@
         <f>IFERROR(AVERAGE(OFFSET(基金配息紀錄!F20,MAX(0,COUNT(基金配息紀錄!F20:F51)-3),0,MIN(3,COUNT(基金配息紀錄!F20:F51)),1)),0)</f>
         <v/>
       </c>
-      <c r="D11" s="117" t="inlineStr">
+      <c r="D11" s="202" t="inlineStr">
         <is>
           <t>取「基金配息紀錄」最近3個有資料的月份實收台幣平均，取代固定假設利率估算</t>
         </is>
@@ -21596,6 +21693,7 @@
       </c>
       <c r="D12" s="128" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14" ht="21.75" customHeight="1" s="113">
       <c r="A14" s="124" t="inlineStr">
         <is>
@@ -21700,7 +21798,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="113">
+    <row r="20" ht="32" customHeight="1" s="113">
       <c r="A20" s="17" t="n">
         <v>5</v>
       </c>
@@ -21712,7 +21810,7 @@
       <c r="C20" s="186" t="n">
         <v>-1651</v>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="204" t="inlineStr">
         <is>
           <t>平準型，保額1044萬(25年)；總保費82萬9249元，與弟弟共同分攤，本人負擔41萬4625元</t>
         </is>
@@ -21772,7 +21870,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="113">
+    <row r="24" ht="32" customHeight="1" s="113">
       <c r="A24" s="17" t="n">
         <v>9</v>
       </c>
@@ -21785,7 +21883,7 @@
         <f>-育兒費!F66</f>
         <v/>
       </c>
-      <c r="D24" s="117" t="inlineStr">
+      <c r="D24" s="202" t="inlineStr">
         <is>
           <t>教育費＋醫療費＋保險費，與前妻各半均攤，取近12個月平均（保費實際由每月現金流支付，已併入計算）</t>
         </is>
@@ -21923,6 +22021,7 @@
       </c>
       <c r="D32" s="128" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34" ht="21.75" customHeight="1" s="113">
       <c r="A34" s="124" t="inlineStr">
         <is>
@@ -21975,9 +22074,13 @@
   <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25"/>
   <cols>
-    <col width="5" customWidth="1" style="113" min="1" max="1"/>
-    <col width="18" customWidth="1" style="113" min="2" max="2"/>
+    <col width="6" customWidth="1" style="113" min="1" max="1"/>
+    <col width="20" customWidth="1" style="113" min="2" max="2"/>
     <col width="10" customWidth="1" style="113" min="3" max="7"/>
+    <col width="13" customWidth="1" style="113" min="4" max="4"/>
+    <col width="13" customWidth="1" style="113" min="5" max="5"/>
+    <col width="13" customWidth="1" style="113" min="6" max="6"/>
+    <col width="13" customWidth="1" style="113" min="7" max="7"/>
     <col width="24" customWidth="1" style="113" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -21995,6 +22098,7 @@
       <c r="G1" s="115" t="n"/>
       <c r="H1" s="116" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3" ht="21.75" customHeight="1" s="113">
       <c r="A3" s="124" t="inlineStr">
         <is>
@@ -22197,6 +22301,7 @@
       <c r="G12" s="169" t="n"/>
       <c r="H12" s="117" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14" ht="21.75" customHeight="1" s="113">
       <c r="A14" s="124" t="inlineStr">
         <is>
@@ -22275,6 +22380,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="113">
       <c r="A18" s="122" t="inlineStr">
         <is>
@@ -22320,6 +22426,7 @@
         <v/>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="21.75" customHeight="1" s="113">
       <c r="A21" s="124" t="inlineStr">
         <is>
@@ -22687,6 +22794,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39" ht="21.75" customHeight="1" s="113">
       <c r="A39" s="124" t="inlineStr">
         <is>
@@ -22720,8 +22828,8 @@
     <mergeCell ref="E32:H32"/>
     <mergeCell ref="E22:H22"/>
     <mergeCell ref="E33:H33"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A37:H37"/>
     <mergeCell ref="E24:H24"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A21:H21"/>

--- a/財務管理系統.xlsx
+++ b/財務管理系統.xlsx
@@ -30,7 +30,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;-$&quot;#,##0;\-"/>
     <numFmt numFmtId="166" formatCode="&quot;-$&quot;#,##0;&quot;-$&quot;#,##0;\-"/>
@@ -39,8 +39,9 @@
     <numFmt numFmtId="169" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="170" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="171" formatCode="0.000"/>
+    <numFmt numFmtId="172" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="49">
+  <fonts count="54">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -366,6 +367,31 @@
       <color rgb="FF000000"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -583,7 +609,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="224">
+  <cellXfs count="230">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1220,6 +1246,24 @@
     <xf numFmtId="0" fontId="29" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="51" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="51" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="52" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="53" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1513,7 +1557,7 @@
       </c>
       <c r="C2" s="111" t="inlineStr">
         <is>
-          <t>2026-09-17 12:19</t>
+          <t>2026-09-18 02:01</t>
         </is>
       </c>
       <c r="D2" s="148" t="inlineStr">
@@ -1522,6 +1566,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="21.75" customHeight="1" s="134">
       <c r="A4" s="135" t="inlineStr">
         <is>
@@ -1601,6 +1646,7 @@
       </c>
       <c r="D8" s="147" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="21.75" customHeight="1" s="134">
       <c r="A10" s="135" t="inlineStr">
         <is>
@@ -1698,6 +1744,7 @@
       <c r="E15" s="141" t="n"/>
       <c r="F15" s="142" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17" ht="21.75" customHeight="1" s="134">
       <c r="A17" s="135" t="inlineStr">
         <is>
@@ -1780,6 +1827,7 @@
       <c r="E22" s="141" t="n"/>
       <c r="F22" s="142" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24" ht="21.75" customHeight="1" s="134">
       <c r="A24" s="135" t="inlineStr">
         <is>
@@ -1822,6 +1870,7 @@
       <c r="E27" s="141" t="n"/>
       <c r="F27" s="142" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29" ht="21.75" customHeight="1" s="134">
       <c r="A29" s="135" t="inlineStr">
         <is>
@@ -1862,6 +1911,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="146" t="inlineStr">
         <is>
@@ -1886,11 +1936,12 @@
           <t>資料來源</t>
         </is>
       </c>
-      <c r="C37" s="133">
+      <c r="C37" s="224">
         <f>資產負債表!C40</f>
         <v/>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="118" t="n"/>
       <c r="B39" s="118" t="n"/>
@@ -1949,7 +2000,7 @@
     <col width="11" customWidth="1" style="134" min="1" max="4"/>
     <col width="12" customWidth="1" style="134" min="5" max="6"/>
     <col width="16" customWidth="1" style="134" min="7" max="7"/>
-    <col width="34.6640625" customWidth="1" style="134" min="8" max="8"/>
+    <col width="34.7" customWidth="1" style="134" min="8" max="8"/>
     <col width="3" customWidth="1" style="134" min="9" max="10"/>
     <col width="11" customWidth="1" style="134" min="11" max="11"/>
     <col width="10" customWidth="1" style="134" min="12" max="12"/>
@@ -1980,6 +2031,7 @@
       <c r="O1" s="136" t="n"/>
       <c r="P1" s="137" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3" ht="21.75" customHeight="1" s="134">
       <c r="A3" s="135" t="inlineStr">
         <is>
@@ -2030,6 +2082,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="21.75" customHeight="1" s="134">
       <c r="A9" s="135" t="inlineStr">
         <is>
@@ -15868,7 +15921,6 @@
   <autoFilter ref="K11:N633"/>
   <mergeCells count="17">
     <mergeCell ref="A9:H9"/>
-    <mergeCell ref="B72:H72"/>
     <mergeCell ref="B7:P7"/>
     <mergeCell ref="B6:P6"/>
     <mergeCell ref="A66:C66"/>
@@ -15878,10 +15930,11 @@
     <mergeCell ref="B5:P5"/>
     <mergeCell ref="B69:H69"/>
     <mergeCell ref="B70:H70"/>
+    <mergeCell ref="B4:P4"/>
     <mergeCell ref="A68:H68"/>
     <mergeCell ref="G66:H66"/>
     <mergeCell ref="A3:P3"/>
-    <mergeCell ref="B4:P4"/>
+    <mergeCell ref="B72:H72"/>
     <mergeCell ref="K10:N10"/>
     <mergeCell ref="K9:N9"/>
   </mergeCells>
@@ -15928,6 +15981,7 @@
       <c r="C1" s="136" t="n"/>
       <c r="D1" s="137" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="134">
       <c r="A3" s="168" t="inlineStr">
         <is>
@@ -15947,6 +16001,7 @@
       <c r="C4" s="141" t="n"/>
       <c r="D4" s="142" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="134">
       <c r="A6" s="166" t="inlineStr">
         <is>
@@ -15960,6 +16015,7 @@
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="21.75" customHeight="1" s="134">
       <c r="A9" s="135" t="inlineStr">
         <is>
@@ -16316,6 +16372,7 @@
         <v/>
       </c>
     </row>
+    <row r="29"/>
     <row r="30" ht="21.75" customHeight="1" s="134">
       <c r="A30" s="135" t="inlineStr">
         <is>
@@ -16378,6 +16435,7 @@
         <v/>
       </c>
     </row>
+    <row r="35"/>
     <row r="36" ht="21.75" customHeight="1" s="134">
       <c r="A36" s="135" t="inlineStr">
         <is>
@@ -16397,6 +16455,7 @@
       <c r="C37" s="141" t="n"/>
       <c r="D37" s="142" t="n"/>
     </row>
+    <row r="38"/>
     <row r="39" ht="36" customHeight="1" s="134">
       <c r="A39" s="138" t="inlineStr">
         <is>
@@ -16458,6 +16517,7 @@
       <c r="D1" s="136" t="n"/>
       <c r="E1" s="137" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3" ht="21.75" customHeight="1" s="134">
       <c r="A3" s="135" t="inlineStr">
         <is>
@@ -16490,6 +16550,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="21.75" customHeight="1" s="134">
       <c r="A8" s="135" t="inlineStr">
         <is>
@@ -16680,6 +16741,7 @@
     <col width="13" customWidth="1" style="134" min="3" max="3"/>
     <col width="18" customWidth="1" style="134" min="4" max="4"/>
     <col width="13" customWidth="1" style="134" min="5" max="6"/>
+    <col width="13" customWidth="1" style="134" min="6" max="6"/>
     <col width="16" customWidth="1" style="134" min="7" max="7"/>
     <col width="36" customWidth="1" style="134" min="8" max="8"/>
   </cols>
@@ -16762,7 +16824,7 @@
       <c r="G5" s="116" t="n">
         <v>23382175.16</v>
       </c>
-      <c r="H5" s="119" t="inlineStr">
+      <c r="H5" s="225" t="inlineStr">
         <is>
           <t>手動（重新設計當天回填）</t>
         </is>
@@ -16790,21 +16852,39 @@
       <c r="G6" s="116" t="n">
         <v>23529678</v>
       </c>
-      <c r="H6" s="119" t="inlineStr">
+      <c r="H6" s="225" t="inlineStr">
         <is>
           <t>MoneyDJ／Frankfurter歐洲央行參考匯率(備援)（每日自動）</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="117" t="n"/>
-      <c r="B7" s="117" t="n"/>
-      <c r="C7" s="117" t="n"/>
-      <c r="D7" s="117" t="n"/>
-      <c r="E7" s="117" t="n"/>
-      <c r="F7" s="117" t="n"/>
-      <c r="G7" s="117" t="n"/>
-      <c r="H7" s="117" t="n"/>
+    <row r="7" ht="30" customHeight="1" s="134">
+      <c r="A7" s="179" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B7" s="115" t="n">
+        <v>73.29000000000001</v>
+      </c>
+      <c r="C7" s="115" t="n">
+        <v>31.864</v>
+      </c>
+      <c r="D7" s="116" t="n">
+        <v>18143492</v>
+      </c>
+      <c r="E7" s="116" t="n">
+        <v>48782776</v>
+      </c>
+      <c r="F7" s="116" t="n">
+        <v>25196830</v>
+      </c>
+      <c r="G7" s="116" t="n">
+        <v>23585945</v>
+      </c>
+      <c r="H7" s="225" t="inlineStr">
+        <is>
+          <t>MoneyDJ／Frankfurter歐洲央行參考匯率(備援)（每日自動）</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="117" t="n"/>
@@ -17061,6 +17141,7 @@
       <c r="C1" s="136" t="n"/>
       <c r="D1" s="137" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3" ht="21.75" customHeight="1" s="134">
       <c r="A3" s="135" t="inlineStr">
         <is>
@@ -17079,7 +17160,7 @@
         </is>
       </c>
       <c r="C4" s="180" t="n">
-        <v>73.15000000000001</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="D4" s="166" t="inlineStr">
         <is>
@@ -17095,7 +17176,7 @@
         </is>
       </c>
       <c r="C5" s="105" t="n">
-        <v>31.858</v>
+        <v>31.864</v>
       </c>
       <c r="D5" s="166" t="inlineStr">
         <is>
@@ -17103,6 +17184,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="21.75" customHeight="1" s="134">
       <c r="A7" s="135" t="inlineStr">
         <is>
@@ -17196,7 +17278,7 @@
         </is>
       </c>
       <c r="C12" s="181" t="n">
-        <v>2089834</v>
+        <v>2108034</v>
       </c>
       <c r="D12" s="120" t="inlineStr">
         <is>
@@ -17252,6 +17334,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="21.75" customHeight="1" s="134">
       <c r="A17" s="135" t="inlineStr">
         <is>
@@ -17426,6 +17509,7 @@
       </c>
       <c r="D26" s="155" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28" ht="21.75" customHeight="1" s="134">
       <c r="A28" s="135" t="inlineStr">
         <is>
@@ -17483,6 +17567,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33" ht="21.75" customHeight="1" s="134">
       <c r="A33" s="135" t="inlineStr">
         <is>
@@ -17514,6 +17599,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="146" t="inlineStr">
         <is>
@@ -17529,7 +17615,7 @@
       </c>
       <c r="C39" s="152" t="inlineStr">
         <is>
-          <t>2026-09-17 12:19</t>
+          <t>2026-09-18 02:01</t>
         </is>
       </c>
     </row>
@@ -17605,6 +17691,7 @@
     <col width="13" customWidth="1" style="134" min="8" max="8"/>
     <col width="10" customWidth="1" style="134" min="9" max="9"/>
     <col width="13" customWidth="1" style="134" min="10" max="11"/>
+    <col width="13" customWidth="1" style="134" min="11" max="11"/>
     <col width="14" customWidth="1" style="134" min="12" max="12"/>
     <col width="50" customWidth="1" style="134" min="13" max="13"/>
   </cols>
@@ -17628,6 +17715,7 @@
       <c r="L1" s="136" t="n"/>
       <c r="M1" s="137" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3" ht="21.75" customHeight="1" s="134">
       <c r="A3" s="135" t="inlineStr">
         <is>
@@ -18005,6 +18093,7 @@
       </c>
       <c r="M10" s="155" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12" ht="21.75" customHeight="1" s="134">
       <c r="A12" s="135" t="inlineStr">
         <is>
@@ -18201,6 +18290,7 @@
       </c>
       <c r="M16" s="155" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18" ht="21.75" customHeight="1" s="134">
       <c r="A18" s="135" t="inlineStr">
         <is>
@@ -18242,6 +18332,7 @@
       <c r="L19" s="155" t="n"/>
       <c r="M19" s="155" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21" ht="21.75" customHeight="1" s="134">
       <c r="A21" s="135" t="inlineStr">
         <is>
@@ -18324,6 +18415,7 @@
     <col width="7" customWidth="1" style="134" min="1" max="1"/>
     <col width="11" customWidth="1" style="134" min="2" max="2"/>
     <col width="13" customWidth="1" style="134" min="3" max="4"/>
+    <col width="13" customWidth="1" style="134" min="4" max="4"/>
     <col width="11" customWidth="1" style="134" min="5" max="5"/>
     <col width="13" customWidth="1" style="134" min="6" max="6"/>
     <col width="14" customWidth="1" style="134" min="7" max="7"/>
@@ -18931,6 +19023,7 @@
       <c r="K16" s="155" t="n"/>
       <c r="L16" s="155" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18" ht="21.75" customHeight="1" s="134">
       <c r="A18" s="135" t="inlineStr">
         <is>
@@ -20292,6 +20385,7 @@
         <v/>
       </c>
     </row>
+    <row r="52"/>
     <row r="53" ht="21.75" customHeight="1" s="134">
       <c r="A53" s="135" t="inlineStr">
         <is>
@@ -20345,6 +20439,7 @@
         <v/>
       </c>
     </row>
+    <row r="55"/>
     <row r="56" ht="21.75" customHeight="1" s="134">
       <c r="A56" s="135" t="inlineStr">
         <is>
@@ -20452,6 +20547,8 @@
   <cols>
     <col width="6" customWidth="1" style="134" min="1" max="1"/>
     <col width="10" customWidth="1" style="134" min="2" max="4"/>
+    <col width="13" customWidth="1" style="134" min="3" max="3"/>
+    <col width="13" customWidth="1" style="134" min="4" max="4"/>
     <col width="11" customWidth="1" style="134" min="5" max="5"/>
     <col width="9" customWidth="1" style="134" min="6" max="6"/>
     <col width="13" customWidth="1" style="134" min="7" max="7"/>
@@ -20474,6 +20571,7 @@
       <c r="H1" s="136" t="n"/>
       <c r="I1" s="137" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3" ht="21.75" customHeight="1" s="134">
       <c r="A3" s="135" t="inlineStr">
         <is>
@@ -20853,6 +20951,7 @@
       <c r="H14" s="155" t="n"/>
       <c r="I14" s="155" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16" ht="21.75" customHeight="1" s="134">
       <c r="A16" s="135" t="inlineStr">
         <is>
@@ -21032,6 +21131,7 @@
       <c r="H21" s="155" t="n"/>
       <c r="I21" s="155" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23" ht="21.75" customHeight="1" s="134">
       <c r="A23" s="135" t="inlineStr">
         <is>
@@ -21069,6 +21169,7 @@
       <c r="H24" s="141" t="n"/>
       <c r="I24" s="142" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26" ht="21.75" customHeight="1" s="134">
       <c r="A26" s="135" t="inlineStr">
         <is>
@@ -21123,6 +21224,10 @@
     <col width="26" customWidth="1" style="134" min="2" max="2"/>
     <col width="12" customWidth="1" style="134" min="3" max="3"/>
     <col width="14" customWidth="1" style="134" min="4" max="8"/>
+    <col width="13" customWidth="1" style="134" min="5" max="5"/>
+    <col width="13" customWidth="1" style="134" min="6" max="6"/>
+    <col width="13" customWidth="1" style="134" min="7" max="7"/>
+    <col width="13" customWidth="1" style="134" min="8" max="8"/>
     <col width="30" customWidth="1" style="134" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -21140,6 +21245,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="134">
       <c r="A4" s="123" t="inlineStr">
         <is>
@@ -21198,24 +21304,24 @@
           <t>元大台灣50</t>
         </is>
       </c>
-      <c r="C5" s="125" t="n">
+      <c r="C5" s="226" t="n">
         <v>8000</v>
       </c>
-      <c r="D5" s="126" t="n">
+      <c r="D5" s="227" t="n">
         <v>64.92</v>
       </c>
-      <c r="E5" s="126" t="n">
-        <v>106.9</v>
-      </c>
-      <c r="F5" s="127" t="n">
-        <v>855200</v>
-      </c>
-      <c r="G5" s="127" t="n">
-        <v>335840</v>
+      <c r="E5" s="227" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="F5" s="228" t="n">
+        <v>864400</v>
+      </c>
+      <c r="G5" s="228" t="n">
+        <v>345040</v>
       </c>
       <c r="H5" s="128" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I5" s="129" t="inlineStr">
@@ -21235,24 +21341,24 @@
           <t>富邦科技</t>
         </is>
       </c>
-      <c r="C6" s="125" t="n">
+      <c r="C6" s="226" t="n">
         <v>12000</v>
       </c>
-      <c r="D6" s="126" t="n">
+      <c r="D6" s="227" t="n">
         <v>35.66</v>
       </c>
-      <c r="E6" s="126" t="n">
-        <v>61.95</v>
-      </c>
-      <c r="F6" s="127" t="n">
-        <v>743400</v>
-      </c>
-      <c r="G6" s="127" t="n">
-        <v>315480</v>
+      <c r="E6" s="227" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="F6" s="228" t="n">
+        <v>752400</v>
+      </c>
+      <c r="G6" s="228" t="n">
+        <v>324480</v>
       </c>
       <c r="H6" s="128" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I6" s="129" t="inlineStr">
@@ -21272,19 +21378,19 @@
           <t>摩根新興科技基金-一般型</t>
         </is>
       </c>
-      <c r="C7" s="125" t="n">
+      <c r="C7" s="226" t="n">
         <v>1091</v>
       </c>
-      <c r="D7" s="126" t="n">
+      <c r="D7" s="227" t="n">
         <v>485.79</v>
       </c>
-      <c r="E7" s="126" t="n">
+      <c r="E7" s="227" t="n">
         <v>450.26</v>
       </c>
-      <c r="F7" s="127" t="n">
+      <c r="F7" s="228" t="n">
         <v>491234</v>
       </c>
-      <c r="G7" s="127" t="n">
+      <c r="G7" s="228" t="n">
         <v>-38763</v>
       </c>
       <c r="H7" s="128" t="inlineStr">
@@ -21304,11 +21410,11 @@
           <t>小計</t>
         </is>
       </c>
-      <c r="F8" s="131">
+      <c r="F8" s="229">
         <f>SUM(F5:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="131">
+      <c r="G8" s="229">
         <f>SUM(G5:G7)</f>
         <v/>
       </c>
@@ -21348,6 +21454,7 @@
       <c r="C1" s="136" t="n"/>
       <c r="D1" s="137" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3" ht="21.75" customHeight="1" s="134">
       <c r="A3" s="135" t="inlineStr">
         <is>
@@ -21495,6 +21602,7 @@
       </c>
       <c r="D12" s="155" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14" ht="21.75" customHeight="1" s="134">
       <c r="A14" s="135" t="inlineStr">
         <is>
@@ -21822,6 +21930,7 @@
       </c>
       <c r="D32" s="155" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34" ht="21.75" customHeight="1" s="134">
       <c r="A34" s="135" t="inlineStr">
         <is>
@@ -21878,6 +21987,9 @@
     <col width="20" customWidth="1" style="134" min="2" max="2"/>
     <col width="10" customWidth="1" style="134" min="3" max="3"/>
     <col width="13" customWidth="1" style="134" min="4" max="7"/>
+    <col width="13" customWidth="1" style="134" min="5" max="5"/>
+    <col width="13" customWidth="1" style="134" min="6" max="6"/>
+    <col width="13" customWidth="1" style="134" min="7" max="7"/>
     <col width="24" customWidth="1" style="134" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -21895,6 +22007,7 @@
       <c r="G1" s="136" t="n"/>
       <c r="H1" s="137" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3" ht="21.75" customHeight="1" s="134">
       <c r="A3" s="135" t="inlineStr">
         <is>
@@ -22097,6 +22210,7 @@
       <c r="G12" s="192" t="n"/>
       <c r="H12" s="140" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14" ht="21.75" customHeight="1" s="134">
       <c r="A14" s="135" t="inlineStr">
         <is>
@@ -22175,6 +22289,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="134">
       <c r="A18" s="168" t="inlineStr">
         <is>
@@ -22220,6 +22335,7 @@
         <v/>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="21.75" customHeight="1" s="134">
       <c r="A21" s="135" t="inlineStr">
         <is>
@@ -22587,6 +22703,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39" ht="21.75" customHeight="1" s="134">
       <c r="A39" s="135" t="inlineStr">
         <is>

--- a/財務管理系統.xlsx
+++ b/財務管理系統.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="貸款總覽" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="育兒費" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請款單" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="股票投資" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="他人股票投資" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="請款單月份清單">'育兒費'!$A$12:$A$62</definedName>
@@ -16118,7 +16118,6 @@
   <autoFilter ref="K11:N633"/>
   <mergeCells count="17">
     <mergeCell ref="A9:H9"/>
-    <mergeCell ref="B72:H72"/>
     <mergeCell ref="B7:P7"/>
     <mergeCell ref="B6:P6"/>
     <mergeCell ref="A66:C66"/>
@@ -16133,6 +16132,7 @@
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="B4:P4"/>
     <mergeCell ref="K10:N10"/>
+    <mergeCell ref="B72:H72"/>
     <mergeCell ref="K9:N9"/>
   </mergeCells>
   <dataValidations count="2">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="B15" s="142" t="n"/>
       <c r="C15" s="240">
-        <f>股票投資!C24</f>
+        <f>他人股票投資!C24</f>
         <v/>
       </c>
       <c r="D15" s="161" t="inlineStr">
@@ -22203,9 +22203,9 @@
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="E32:H32"/>
     <mergeCell ref="E22:H22"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="E33:H33"/>
     <mergeCell ref="A37:H37"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="A18:B18"/>
     <mergeCell ref="E24:H24"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A21:H21"/>
